--- a/xlsx/fluxo_caixa/realizado_latest.xlsx
+++ b/xlsx/fluxo_caixa/realizado_latest.xlsx
@@ -33,7 +33,7 @@
     <t>Período de Lançamento</t>
   </si>
   <si>
-    <t>01/10/2026 até 11/10/2026</t>
+    <t>01/10/2026 até 12/10/2026</t>
   </si>
   <si>
     <t>Período de Competência</t>
